--- a/Links de Variables Macro.xlsx
+++ b/Links de Variables Macro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dddma\OneDrive\Escritorio\Codigos_repors\data_verso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781DFDD5-2083-4462-BAAA-E87FF8C30C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F6AC8-5054-42FA-BABD-E2F0C2F8F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1252,7 +1252,7 @@
       <c r="A11" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="23" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="3" t="s">

--- a/Links de Variables Macro.xlsx
+++ b/Links de Variables Macro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dddma\OneDrive\Escritorio\Codigos_repors\data_verso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F6AC8-5054-42FA-BABD-E2F0C2F8F35F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70581451-4852-4FC5-A528-DB68CDC391AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1238,7 +1238,7 @@
       <c r="A10" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="23" t="s">
         <v>34</v>
       </c>
       <c r="C10" s="3" t="s">

--- a/Links de Variables Macro.xlsx
+++ b/Links de Variables Macro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dddma\OneDrive\Escritorio\Codigos_repors\data_verso\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70581451-4852-4FC5-A528-DB68CDC391AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BAEAE9-4165-4E44-8A84-E70AD79122D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="135">
   <si>
     <t xml:space="preserve">Variables </t>
   </si>
@@ -437,6 +437,12 @@
   </si>
   <si>
     <t xml:space="preserve">revoisar el documento enviado por pasante 1 CIUS para la creacion de las tablas, ahi esta el paso a paso y la referencia del modelo de base de datos </t>
+  </si>
+  <si>
+    <t>https://appscvsmovil.supercias.gob.ec/ranking/reporte.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supercias Utilidad </t>
   </si>
 </sst>
 </file>
@@ -702,7 +708,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,9 +795,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1151,7 +1154,7 @@
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="40" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1266,7 +1269,7 @@
       <c r="A12" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="23" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1280,7 +1283,7 @@
       <c r="A13" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>131</v>
       </c>
       <c r="C13" t="s">
@@ -1289,7 +1292,7 @@
       <c r="D13" s="13"/>
     </row>
     <row r="14" spans="1:5" s="2" customFormat="1" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="39" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="3"/>
@@ -1328,7 +1331,7 @@
       <c r="A17" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="45" t="s">
         <v>14</v>
       </c>
       <c r="C17" s="9" t="s">
@@ -1380,17 +1383,22 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="39" t="s">
+      <c r="D21" s="38" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
-      <c r="D22" s="39"/>
+      <c r="A22" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="38"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="25"/>
-      <c r="D23" s="39"/>
+      <c r="D23" s="38"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="25"/>
@@ -1618,10 +1626,10 @@
       </c>
     </row>
     <row r="40" spans="2:4" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="B40" s="44" t="s">
+      <c r="B40" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="C40" s="45" t="s">
+      <c r="C40" s="44" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1634,14 +1642,14 @@
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B42" s="42"/>
-      <c r="C42" s="43"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="42"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>37</v>
       </c>
-      <c r="C43" s="43"/>
+      <c r="C43" s="42"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B45" s="27" t="s">
@@ -1751,7 +1759,7 @@
       </c>
     </row>
     <row r="67" spans="2:3" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B67" s="47" t="s">
+      <c r="B67" s="46" t="s">
         <v>125</v>
       </c>
       <c r="C67" s="35" t="s">
